--- a/safe_drawer_log.xlsx
+++ b/safe_drawer_log.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sep 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Oct 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — September 2026</t>
+          <t>Five Guys 2065 — Safe &amp; Drawer Count Log — October 2026</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Tue 09/01</t>
+          <t>Thu 10/01</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -607,7 +607,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Wed 09/02</t>
+          <t>Fri 10/02</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -628,101 +628,101 @@
       <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Thu 09/03</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10/03</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Fri 09/04</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Sun 10/04</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Sat 09/05</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="6" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10/05</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Sun 09/06</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="6" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Tue 10/06</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Mon 09/07</t>
+          <t>Wed 10/07</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -745,7 +745,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Tue 09/08</t>
+          <t>Thu 10/08</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -768,7 +768,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Wed 09/09</t>
+          <t>Fri 10/09</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -789,101 +789,101 @@
       <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Thu 09/10</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10/10</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Fri 09/11</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Sun 10/11</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Sat 09/12</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10/12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Sun 09/13</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="6" t="n"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tue 10/13</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mon 09/14</t>
+          <t>Wed 10/14</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Tue 09/15</t>
+          <t>Thu 10/15</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -929,7 +929,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Wed 09/16</t>
+          <t>Fri 10/16</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -950,101 +950,101 @@
       <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Thu 09/17</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="4" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10/17</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Fri 09/18</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="4" t="n"/>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Sun 10/18</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Sat 09/19</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="6" t="n"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10/19</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Sun 09/20</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="6" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Tue 10/20</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Mon 09/21</t>
+          <t>Wed 10/21</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1067,7 +1067,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Tue 09/22</t>
+          <t>Thu 10/22</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1090,7 +1090,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Wed 09/23</t>
+          <t>Fri 10/23</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1111,101 +1111,101 @@
       <c r="K26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Thu 09/24</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="4" t="n"/>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10/24</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Fri 09/25</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Sun 10/25</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="6" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Sat 09/26</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="6" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10/26</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Sun 09/27</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="7" t="n">
-        <v>700</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>200</v>
-      </c>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="6" t="n"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tue 10/27</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Mon 09/28</t>
+          <t>Wed 10/28</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1228,7 +1228,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Tue 09/29</t>
+          <t>Thu 10/29</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1251,7 +1251,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Wed 09/30</t>
+          <t>Fri 10/30</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1271,18 +1271,41 @@
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="4" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Sat 10/31</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="6" t="n"/>
+      <c r="I34" s="7" t="n"/>
+      <c r="J34" s="7" t="n"/>
+      <c r="K34" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>MONTH TOTALS</t>
         </is>
       </c>
-      <c r="I35" s="9">
-        <f>SUM(I4:I33)</f>
+      <c r="I36" s="9">
+        <f>SUM(I4:I34)</f>
         <v/>
       </c>
-      <c r="J35" s="9">
-        <f>SUM(J4:J33)</f>
+      <c r="J36" s="9">
+        <f>SUM(J4:J34)</f>
         <v/>
       </c>
     </row>
